--- a/底层协议/新遥控器数据下载与控制协议.xlsx
+++ b/底层协议/新遥控器数据下载与控制协议.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Engineer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SJGK8\Desktop\PROJECT\太阳能遥控器app\底层协议\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173C3BED-7669-40DB-B77A-988057DFE9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25EB8AC-9776-48FB-87B5-821E35D66152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="251">
   <si>
     <t>主机地址码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1263,6 +1263,14 @@
   </si>
   <si>
     <t>RF例：0xff 0xce，0X06，0，0x0E,0x01,0,0x30,SUM   示例为读状态指令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FF CE 06 00 0D 00 00 30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1517,7 +1525,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1584,41 +1592,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1641,59 +1655,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2026,24 +2028,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -2215,7 +2217,7 @@
       <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="49" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -2238,7 +2240,7 @@
       <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="23"/>
+      <c r="D12" s="49"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>1</v>
@@ -2248,16 +2250,16 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="42">
+      <c r="A13" s="22">
         <v>10</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="46" t="s">
         <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -2271,14 +2273,14 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A14" s="42">
+      <c r="A14" s="22">
         <v>11</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="42" t="s">
+      <c r="B14" s="34"/>
+      <c r="C14" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="44"/>
+      <c r="D14" s="46"/>
       <c r="E14" s="4"/>
       <c r="F14" s="2">
         <v>1</v>
@@ -2330,241 +2332,241 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="42">
+      <c r="A17" s="22">
         <v>14</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="54"/>
-      <c r="F17" s="42">
+      <c r="E17" s="25"/>
+      <c r="F17" s="22">
         <v>1</v>
       </c>
       <c r="G17">
         <v>14</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="I17" s="58" t="s">
+      <c r="I17" s="30" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A18" s="42">
+    <row r="18" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A18" s="22">
         <v>15</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="54"/>
-      <c r="F18" s="42">
-        <v>1</v>
-      </c>
-      <c r="G18" s="55">
+      <c r="E18" s="25"/>
+      <c r="F18" s="22">
+        <v>1</v>
+      </c>
+      <c r="G18" s="26">
         <v>15</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="58"/>
-    </row>
-    <row r="19" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A19" s="42">
+      <c r="H18" s="29"/>
+      <c r="I18" s="30"/>
+    </row>
+    <row r="19" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A19" s="22">
         <v>16</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="42">
-        <v>1</v>
-      </c>
-      <c r="G19" s="55">
+      <c r="E19" s="25"/>
+      <c r="F19" s="22">
+        <v>1</v>
+      </c>
+      <c r="G19" s="26">
         <v>16</v>
       </c>
-      <c r="H19" s="57"/>
-      <c r="I19" s="58"/>
-    </row>
-    <row r="20" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="42">
+      <c r="H19" s="29"/>
+      <c r="I19" s="30"/>
+    </row>
+    <row r="20" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="22">
         <v>17</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="54"/>
-      <c r="F20" s="42">
-        <v>1</v>
-      </c>
-      <c r="G20" s="55">
+      <c r="E20" s="25"/>
+      <c r="F20" s="22">
+        <v>1</v>
+      </c>
+      <c r="G20" s="26">
         <v>17</v>
       </c>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
-    </row>
-    <row r="21" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="42">
+      <c r="H20" s="29"/>
+      <c r="I20" s="30"/>
+    </row>
+    <row r="21" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A21" s="22">
         <v>18</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="54"/>
-      <c r="F21" s="42">
-        <v>1</v>
-      </c>
-      <c r="G21" s="55">
+      <c r="E21" s="25"/>
+      <c r="F21" s="22">
+        <v>1</v>
+      </c>
+      <c r="G21" s="26">
         <v>18</v>
       </c>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-    </row>
-    <row r="22" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="42">
+      <c r="H21" s="29"/>
+      <c r="I21" s="30"/>
+    </row>
+    <row r="22" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A22" s="22">
         <v>19</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E22" s="54"/>
-      <c r="F22" s="42">
-        <v>1</v>
-      </c>
-      <c r="G22" s="55">
+      <c r="E22" s="25"/>
+      <c r="F22" s="22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="26">
         <v>19</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="24" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A23" s="42">
+    <row r="23" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A23" s="22">
         <v>20</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="42">
-        <v>1</v>
-      </c>
-      <c r="G23" s="55">
+      <c r="E23" s="25"/>
+      <c r="F23" s="22">
+        <v>1</v>
+      </c>
+      <c r="G23" s="26">
         <v>20</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="24" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="42">
+    <row r="24" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A24" s="22">
         <v>21</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="42">
-        <v>1</v>
-      </c>
-      <c r="G24" s="55">
+      <c r="E24" s="25"/>
+      <c r="F24" s="22">
+        <v>1</v>
+      </c>
+      <c r="G24" s="26">
         <v>21</v>
       </c>
-      <c r="H24" s="52" t="s">
+      <c r="H24" s="24" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A25" s="42">
+    <row r="25" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A25" s="22">
         <v>22</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="42">
-        <v>1</v>
-      </c>
-      <c r="G25" s="55">
+      <c r="E25" s="25"/>
+      <c r="F25" s="22">
+        <v>1</v>
+      </c>
+      <c r="G25" s="26">
         <v>22</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="24" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A26" s="42">
+    <row r="26" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A26" s="22">
         <v>23</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="42">
-        <v>1</v>
-      </c>
-      <c r="G26" s="55">
+      <c r="E26" s="25"/>
+      <c r="F26" s="22">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26">
         <v>23</v>
       </c>
-      <c r="H26" s="52" t="s">
+      <c r="H26" s="24" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2589,27 +2591,27 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A28" s="42">
+    <row r="28" spans="1:9" s="26" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A28" s="22">
         <v>25</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="54"/>
-      <c r="F28" s="42">
-        <v>1</v>
-      </c>
-      <c r="G28" s="55">
+      <c r="E28" s="25"/>
+      <c r="F28" s="22">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26">
         <v>25</v>
       </c>
-      <c r="H28" s="52" t="s">
+      <c r="H28" s="24" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2684,14 +2686,14 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
     </row>
     <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
@@ -2864,7 +2866,7 @@
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="49" t="s">
         <v>27</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -2887,7 +2889,7 @@
       <c r="C43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="23"/>
+      <c r="D43" s="49"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2">
         <v>1</v>
@@ -2897,16 +2899,16 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="42">
+      <c r="A44" s="22">
         <v>10</v>
       </c>
-      <c r="B44" s="43" t="s">
+      <c r="B44" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="D44" s="44" t="s">
+      <c r="D44" s="46" t="s">
         <v>236</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -2920,14 +2922,14 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="42">
+      <c r="A45" s="22">
         <v>11</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="42" t="s">
+      <c r="B45" s="34"/>
+      <c r="C45" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="D45" s="44"/>
+      <c r="D45" s="46"/>
       <c r="E45" s="4"/>
       <c r="F45" s="2">
         <v>1</v>
@@ -2977,204 +2979,202 @@
       <c r="G47">
         <v>13</v>
       </c>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
     </row>
     <row r="48" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A48" s="42">
+      <c r="A48" s="22">
         <v>14</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B48" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="52" t="s">
+      <c r="D48" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="54"/>
-      <c r="F48" s="42">
-        <v>1</v>
-      </c>
-      <c r="G48" s="55">
+      <c r="E48" s="25"/>
+      <c r="F48" s="22">
+        <v>1</v>
+      </c>
+      <c r="G48" s="26">
         <v>14</v>
       </c>
-      <c r="H48" s="56" t="s">
+      <c r="H48" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="I48" s="58" t="s">
+      <c r="I48" s="30" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A49" s="42">
+      <c r="A49" s="22">
         <v>15</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="52" t="s">
+      <c r="D49" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E49" s="54"/>
-      <c r="F49" s="42">
-        <v>1</v>
-      </c>
-      <c r="G49" s="55">
+      <c r="E49" s="25"/>
+      <c r="F49" s="22">
+        <v>1</v>
+      </c>
+      <c r="G49" s="26">
         <v>15</v>
       </c>
-      <c r="H49" s="56"/>
-      <c r="I49" s="58"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="30"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A50" s="42">
+      <c r="A50" s="22">
         <v>16</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="42" t="s">
+      <c r="C50" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="52" t="s">
+      <c r="D50" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E50" s="54"/>
-      <c r="F50" s="42">
-        <v>1</v>
-      </c>
-      <c r="G50" s="55">
+      <c r="E50" s="25"/>
+      <c r="F50" s="22">
+        <v>1</v>
+      </c>
+      <c r="G50" s="26">
         <v>16</v>
       </c>
-      <c r="H50" s="56"/>
-      <c r="I50" s="58"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="30"/>
     </row>
     <row r="51" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A51" s="42">
+      <c r="A51" s="22">
         <v>17</v>
       </c>
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="42" t="s">
+      <c r="C51" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D51" s="52" t="s">
+      <c r="D51" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E51" s="54"/>
-      <c r="F51" s="42">
-        <v>1</v>
-      </c>
-      <c r="G51" s="55">
+      <c r="E51" s="25"/>
+      <c r="F51" s="22">
+        <v>1</v>
+      </c>
+      <c r="G51" s="26">
         <v>17</v>
       </c>
-      <c r="H51" s="56"/>
-      <c r="I51" s="58"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="30"/>
     </row>
     <row r="52" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A52" s="42">
+      <c r="A52" s="22">
         <v>18</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C52" s="42" t="s">
+      <c r="C52" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D52" s="52" t="s">
+      <c r="D52" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E52" s="54"/>
-      <c r="F52" s="42">
-        <v>1</v>
-      </c>
-      <c r="G52" s="55">
+      <c r="E52" s="25"/>
+      <c r="F52" s="22">
+        <v>1</v>
+      </c>
+      <c r="G52" s="26">
         <v>18</v>
       </c>
-      <c r="H52" s="52" t="s">
+      <c r="H52" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="I52" s="48"/>
+      <c r="I52" s="31"/>
     </row>
     <row r="53" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A53" s="42">
+      <c r="A53" s="22">
         <v>19</v>
       </c>
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="42" t="s">
+      <c r="C53" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D53" s="52" t="s">
+      <c r="D53" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E53" s="54"/>
-      <c r="F53" s="42">
-        <v>1</v>
-      </c>
-      <c r="G53" s="55">
+      <c r="E53" s="25"/>
+      <c r="F53" s="22">
+        <v>1</v>
+      </c>
+      <c r="G53" s="26">
         <v>19</v>
       </c>
-      <c r="H53" s="52" t="s">
+      <c r="H53" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="I53" s="47"/>
+      <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A54" s="42">
+      <c r="A54" s="22">
         <v>20</v>
       </c>
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="C54" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D54" s="52" t="s">
+      <c r="D54" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E54" s="54"/>
-      <c r="F54" s="42">
-        <v>1</v>
-      </c>
-      <c r="G54" s="55">
+      <c r="E54" s="25"/>
+      <c r="F54" s="22">
+        <v>1</v>
+      </c>
+      <c r="G54" s="26">
         <v>20</v>
       </c>
-      <c r="H54" s="52" t="s">
+      <c r="H54" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="I54" s="47"/>
+      <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A55" s="42">
+      <c r="A55" s="22">
         <v>21</v>
       </c>
-      <c r="B55" s="42" t="s">
+      <c r="B55" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="42" t="s">
+      <c r="C55" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D55" s="52" t="s">
+      <c r="D55" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E55" s="54"/>
-      <c r="F55" s="42">
-        <v>1</v>
-      </c>
-      <c r="G55" s="55">
+      <c r="E55" s="25"/>
+      <c r="F55" s="22">
+        <v>1</v>
+      </c>
+      <c r="G55" s="26">
         <v>21</v>
       </c>
-      <c r="H55" s="52" t="s">
+      <c r="H55" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="I55" s="47"/>
+      <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
@@ -3261,194 +3261,194 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A60" s="42">
+      <c r="A60" s="22">
         <v>26</v>
       </c>
-      <c r="B60" s="42" t="s">
+      <c r="B60" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="42" t="s">
+      <c r="C60" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D60" s="52" t="s">
+      <c r="D60" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E60" s="54"/>
-      <c r="F60" s="42">
-        <v>1</v>
-      </c>
-      <c r="G60" s="55">
+      <c r="E60" s="25"/>
+      <c r="F60" s="22">
+        <v>1</v>
+      </c>
+      <c r="G60" s="26">
         <v>26</v>
       </c>
-      <c r="H60" s="52" t="s">
+      <c r="H60" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A61" s="42">
+      <c r="A61" s="22">
         <v>27</v>
       </c>
-      <c r="B61" s="42" t="s">
+      <c r="B61" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="42" t="s">
+      <c r="C61" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="52" t="s">
+      <c r="D61" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="54"/>
-      <c r="F61" s="42">
-        <v>1</v>
-      </c>
-      <c r="G61" s="55">
+      <c r="E61" s="25"/>
+      <c r="F61" s="22">
+        <v>1</v>
+      </c>
+      <c r="G61" s="26">
         <v>27</v>
       </c>
-      <c r="H61" s="52" t="s">
+      <c r="H61" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A62" s="42">
+      <c r="A62" s="22">
         <v>28</v>
       </c>
-      <c r="B62" s="42" t="s">
+      <c r="B62" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="42" t="s">
+      <c r="C62" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D62" s="52" t="s">
+      <c r="D62" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="54"/>
-      <c r="F62" s="42">
-        <v>1</v>
-      </c>
-      <c r="G62" s="55">
+      <c r="E62" s="25"/>
+      <c r="F62" s="22">
+        <v>1</v>
+      </c>
+      <c r="G62" s="26">
         <v>28</v>
       </c>
-      <c r="H62" s="52" t="s">
+      <c r="H62" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A63" s="42">
+      <c r="A63" s="22">
         <v>29</v>
       </c>
-      <c r="B63" s="42" t="s">
+      <c r="B63" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="42" t="s">
+      <c r="C63" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="52" t="s">
+      <c r="D63" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="54"/>
-      <c r="F63" s="42">
-        <v>1</v>
-      </c>
-      <c r="G63" s="55">
+      <c r="E63" s="25"/>
+      <c r="F63" s="22">
+        <v>1</v>
+      </c>
+      <c r="G63" s="26">
         <v>29</v>
       </c>
-      <c r="H63" s="52" t="s">
+      <c r="H63" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A64" s="42">
+      <c r="A64" s="22">
         <v>30</v>
       </c>
-      <c r="B64" s="42" t="s">
+      <c r="B64" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C64" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="52" t="s">
+      <c r="D64" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="54"/>
-      <c r="F64" s="42">
-        <v>1</v>
-      </c>
-      <c r="G64" s="55">
+      <c r="E64" s="25"/>
+      <c r="F64" s="22">
+        <v>1</v>
+      </c>
+      <c r="G64" s="26">
         <v>30</v>
       </c>
-      <c r="H64" s="52" t="s">
+      <c r="H64" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A65" s="42">
+      <c r="A65" s="22">
         <v>31</v>
       </c>
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C65" s="42" t="s">
+      <c r="C65" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D65" s="52" t="s">
+      <c r="D65" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E65" s="54"/>
-      <c r="F65" s="42">
-        <v>1</v>
-      </c>
-      <c r="G65" s="55">
+      <c r="E65" s="25"/>
+      <c r="F65" s="22">
+        <v>1</v>
+      </c>
+      <c r="G65" s="26">
         <v>31</v>
       </c>
-      <c r="H65" s="52" t="s">
+      <c r="H65" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A66" s="42">
+      <c r="A66" s="22">
         <v>32</v>
       </c>
-      <c r="B66" s="42" t="s">
+      <c r="B66" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C66" s="42" t="s">
+      <c r="C66" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="52" t="s">
+      <c r="D66" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E66" s="54"/>
-      <c r="F66" s="42">
-        <v>1</v>
-      </c>
-      <c r="G66" s="55">
+      <c r="E66" s="25"/>
+      <c r="F66" s="22">
+        <v>1</v>
+      </c>
+      <c r="G66" s="26">
         <v>32</v>
       </c>
-      <c r="H66" s="52" t="s">
+      <c r="H66" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A67" s="42">
+      <c r="A67" s="22">
         <v>33</v>
       </c>
-      <c r="B67" s="42" t="s">
+      <c r="B67" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C67" s="42" t="s">
+      <c r="C67" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D67" s="52" t="s">
+      <c r="D67" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E67" s="54"/>
-      <c r="F67" s="42">
-        <v>1</v>
-      </c>
-      <c r="G67" s="55">
+      <c r="E67" s="25"/>
+      <c r="F67" s="22">
+        <v>1</v>
+      </c>
+      <c r="G67" s="26">
         <v>33</v>
       </c>
-      <c r="H67" s="52" t="s">
+      <c r="H67" s="24" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3515,14 +3515,17 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="24.75" x14ac:dyDescent="0.15">
-      <c r="A73" s="27" t="s">
+      <c r="A73" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="47"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="47"/>
+      <c r="H73" s="12" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="74" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
@@ -3715,7 +3718,7 @@
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="23" t="s">
+      <c r="D83" s="49" t="s">
         <v>27</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -3738,7 +3741,7 @@
       <c r="C84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D84" s="23"/>
+      <c r="D84" s="49"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2">
         <v>1</v>
@@ -3748,16 +3751,16 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="42">
+      <c r="A85" s="22">
         <v>10</v>
       </c>
-      <c r="B85" s="43" t="s">
+      <c r="B85" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="C85" s="42" t="s">
+      <c r="C85" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="D85" s="44" t="s">
+      <c r="D85" s="46" t="s">
         <v>236</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -3771,14 +3774,14 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="42">
+      <c r="A86" s="22">
         <v>11</v>
       </c>
-      <c r="B86" s="45"/>
-      <c r="C86" s="42" t="s">
+      <c r="B86" s="34"/>
+      <c r="C86" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="D86" s="44"/>
+      <c r="D86" s="46"/>
       <c r="E86" s="4"/>
       <c r="F86" s="2">
         <v>1</v>
@@ -3830,122 +3833,122 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A89" s="42">
+      <c r="A89" s="22">
         <v>15</v>
       </c>
-      <c r="B89" s="42" t="s">
+      <c r="B89" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C89" s="42" t="s">
+      <c r="C89" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D89" s="52" t="s">
+      <c r="D89" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E89" s="54"/>
-      <c r="F89" s="42">
-        <v>1</v>
-      </c>
-      <c r="G89" s="55">
+      <c r="E89" s="25"/>
+      <c r="F89" s="22">
+        <v>1</v>
+      </c>
+      <c r="G89" s="26">
         <v>15</v>
       </c>
-      <c r="H89" s="52" t="s">
+      <c r="H89" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A90" s="42">
+      <c r="A90" s="22">
         <v>16</v>
       </c>
-      <c r="B90" s="42" t="s">
+      <c r="B90" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C90" s="42" t="s">
+      <c r="C90" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D90" s="52" t="s">
+      <c r="D90" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E90" s="54"/>
-      <c r="F90" s="42">
-        <v>1</v>
-      </c>
-      <c r="G90" s="55">
+      <c r="E90" s="25"/>
+      <c r="F90" s="22">
+        <v>1</v>
+      </c>
+      <c r="G90" s="26">
         <v>16</v>
       </c>
-      <c r="H90" s="52" t="s">
+      <c r="H90" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A91" s="42">
+      <c r="A91" s="22">
         <v>17</v>
       </c>
-      <c r="B91" s="42" t="s">
+      <c r="B91" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C91" s="42" t="s">
+      <c r="C91" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D91" s="52" t="s">
+      <c r="D91" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E91" s="54"/>
-      <c r="F91" s="42">
-        <v>1</v>
-      </c>
-      <c r="G91" s="55">
+      <c r="E91" s="25"/>
+      <c r="F91" s="22">
+        <v>1</v>
+      </c>
+      <c r="G91" s="26">
         <v>17</v>
       </c>
-      <c r="H91" s="52" t="s">
+      <c r="H91" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A92" s="42">
+      <c r="A92" s="22">
         <v>18</v>
       </c>
-      <c r="B92" s="42" t="s">
+      <c r="B92" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C92" s="42" t="s">
+      <c r="C92" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="52" t="s">
+      <c r="D92" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="54"/>
-      <c r="F92" s="42">
-        <v>1</v>
-      </c>
-      <c r="G92" s="55">
+      <c r="E92" s="25"/>
+      <c r="F92" s="22">
+        <v>1</v>
+      </c>
+      <c r="G92" s="26">
         <v>18</v>
       </c>
-      <c r="H92" s="52" t="s">
+      <c r="H92" s="24" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A93" s="42">
+      <c r="A93" s="22">
         <v>19</v>
       </c>
-      <c r="B93" s="42" t="s">
+      <c r="B93" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C93" s="42" t="s">
+      <c r="C93" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="52" t="s">
+      <c r="D93" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E93" s="54"/>
-      <c r="F93" s="42">
-        <v>1</v>
-      </c>
-      <c r="G93" s="55">
+      <c r="E93" s="25"/>
+      <c r="F93" s="22">
+        <v>1</v>
+      </c>
+      <c r="G93" s="26">
         <v>19</v>
       </c>
-      <c r="H93" s="52" t="s">
+      <c r="H93" s="24" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4012,14 +4015,14 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="28" t="s">
+      <c r="A99" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="B99" s="28"/>
-      <c r="C99" s="28"/>
-      <c r="D99" s="28"/>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
     </row>
     <row r="100" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
@@ -4122,42 +4125,42 @@
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="32" t="s">
+      <c r="A106" s="55" t="s">
         <v>204</v>
       </c>
-      <c r="B106" s="32"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="32"/>
-      <c r="E106" s="32"/>
-      <c r="F106" s="32"/>
+      <c r="B106" s="55"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
     </row>
     <row r="107" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="33"/>
-      <c r="B107" s="33"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="33"/>
+      <c r="A107" s="56"/>
+      <c r="B107" s="56"/>
+      <c r="C107" s="56"/>
+      <c r="D107" s="56"/>
+      <c r="E107" s="56"/>
+      <c r="F107" s="56"/>
     </row>
     <row r="108" spans="1:6" ht="21" x14ac:dyDescent="0.15">
-      <c r="A108" s="22" t="s">
+      <c r="A108" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
-      <c r="D108" s="22"/>
-      <c r="E108" s="22"/>
-      <c r="F108" s="22"/>
+      <c r="B108" s="50"/>
+      <c r="C108" s="50"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
+      <c r="F108" s="50"/>
     </row>
     <row r="109" spans="1:6" ht="24.75" x14ac:dyDescent="0.15">
-      <c r="A109" s="28" t="s">
+      <c r="A109" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="B109" s="28"/>
-      <c r="C109" s="28"/>
-      <c r="D109" s="28"/>
-      <c r="E109" s="28"/>
-      <c r="F109" s="28"/>
+      <c r="B109" s="48"/>
+      <c r="C109" s="48"/>
+      <c r="D109" s="48"/>
+      <c r="E109" s="48"/>
+      <c r="F109" s="48"/>
     </row>
     <row r="110" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A110" s="2">
@@ -4240,14 +4243,14 @@
       <c r="F114" s="1"/>
     </row>
     <row r="115" spans="1:10" ht="20.25" x14ac:dyDescent="0.15">
-      <c r="A115" s="29" t="s">
+      <c r="A115" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="B115" s="30"/>
-      <c r="C115" s="30"/>
-      <c r="D115" s="30"/>
-      <c r="E115" s="30"/>
-      <c r="F115" s="31"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="52"/>
+      <c r="D115" s="52"/>
+      <c r="E115" s="52"/>
+      <c r="F115" s="53"/>
     </row>
     <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A116" s="2">
@@ -4283,7 +4286,9 @@
       <c r="F117" s="2">
         <v>1</v>
       </c>
-      <c r="H117" s="2"/>
+      <c r="H117" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="118" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A118" s="2">
@@ -4395,14 +4400,14 @@
       <c r="H123" s="2"/>
     </row>
     <row r="124" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A124" s="53" t="s">
+      <c r="A124" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="B124" s="53"/>
-      <c r="C124" s="53"/>
-      <c r="D124" s="53"/>
-      <c r="E124" s="53"/>
-      <c r="F124" s="53"/>
+      <c r="B124" s="54"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="54"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="54"/>
       <c r="H124" s="2"/>
     </row>
     <row r="125" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
@@ -4410,14 +4415,14 @@
       <c r="H125" s="2"/>
     </row>
     <row r="126" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="24" t="s">
+      <c r="A126" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
-      <c r="D126" s="25"/>
-      <c r="E126" s="25"/>
-      <c r="F126" s="26"/>
+      <c r="B126" s="44"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="44"/>
+      <c r="E126" s="44"/>
+      <c r="F126" s="45"/>
       <c r="H126" s="2"/>
     </row>
     <row r="127" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
@@ -4588,13 +4593,13 @@
       <c r="A133" s="2">
         <v>6</v>
       </c>
-      <c r="B133" s="49" t="s">
+      <c r="B133" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="C133" s="49" t="s">
+      <c r="C133" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="D133" s="52" t="s">
+      <c r="D133" s="24" t="s">
         <v>247</v>
       </c>
       <c r="F133" s="2">
@@ -4609,13 +4614,13 @@
       <c r="A134" s="2">
         <v>7</v>
       </c>
-      <c r="B134" s="42" t="s">
+      <c r="B134" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C134" s="42" t="s">
+      <c r="C134" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D134" s="44" t="s">
+      <c r="D134" s="46" t="s">
         <v>243</v>
       </c>
       <c r="E134" s="4"/>
@@ -4631,13 +4636,13 @@
       <c r="A135" s="2">
         <v>8</v>
       </c>
-      <c r="B135" s="42" t="s">
+      <c r="B135" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="C135" s="42" t="s">
+      <c r="C135" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D135" s="44"/>
+      <c r="D135" s="46"/>
       <c r="E135" s="1"/>
       <c r="F135" s="2">
         <v>1</v>
@@ -4650,13 +4655,13 @@
       <c r="A136" s="2">
         <v>9</v>
       </c>
-      <c r="B136" s="42" t="s">
+      <c r="B136" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="C136" s="42" t="s">
+      <c r="C136" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D136" s="44" t="s">
+      <c r="D136" s="46" t="s">
         <v>244</v>
       </c>
       <c r="E136" s="1"/>
@@ -4671,13 +4676,13 @@
       <c r="A137" s="2">
         <v>10</v>
       </c>
-      <c r="B137" s="42" t="s">
+      <c r="B137" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C137" s="42" t="s">
+      <c r="C137" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D137" s="44"/>
+      <c r="D137" s="46"/>
       <c r="E137" s="1"/>
       <c r="F137" s="2">
         <v>1</v>
@@ -4690,13 +4695,13 @@
       <c r="A138" s="2">
         <v>11</v>
       </c>
-      <c r="B138" s="42" t="s">
+      <c r="B138" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C138" s="42" t="s">
+      <c r="C138" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="D138" s="52" t="s">
+      <c r="D138" s="24" t="s">
         <v>242</v>
       </c>
       <c r="E138" s="1"/>
@@ -4711,30 +4716,28 @@
       <c r="A139" s="2">
         <v>12</v>
       </c>
-      <c r="B139" s="49" t="s">
+      <c r="B139" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="C139" s="42" t="s">
+      <c r="C139" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="D139" s="50" t="s">
+      <c r="D139" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="E139" s="41"/>
       <c r="F139" s="7"/>
     </row>
     <row r="140" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A140" s="2">
         <v>13</v>
       </c>
-      <c r="B140" s="49" t="s">
+      <c r="B140" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C140" s="42" t="s">
+      <c r="C140" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D140" s="51"/>
-      <c r="E140" s="41"/>
+      <c r="D140" s="28"/>
       <c r="F140" s="7"/>
     </row>
     <row r="141" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
@@ -4800,14 +4803,14 @@
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A146" s="36" t="s">
+      <c r="A146" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="38"/>
-      <c r="C146" s="38"/>
-      <c r="D146" s="38"/>
-      <c r="E146" s="38"/>
-      <c r="F146" s="37"/>
+      <c r="B146" s="40"/>
+      <c r="C146" s="40"/>
+      <c r="D146" s="40"/>
+      <c r="E146" s="40"/>
+      <c r="F146" s="39"/>
     </row>
     <row r="147" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A147" s="2">
@@ -4816,10 +4819,10 @@
       <c r="B147" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="39" t="s">
+      <c r="C147" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="D147" s="40"/>
+      <c r="D147" s="42"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
     </row>
@@ -4830,10 +4833,10 @@
       <c r="B148" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C148" s="39" t="s">
+      <c r="C148" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="D148" s="40"/>
+      <c r="D148" s="42"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
     </row>
@@ -4844,10 +4847,10 @@
       <c r="B149" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C149" s="39" t="s">
+      <c r="C149" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D149" s="40"/>
+      <c r="D149" s="42"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
     </row>
@@ -4858,10 +4861,10 @@
       <c r="B150" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C150" s="39" t="s">
+      <c r="C150" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="D150" s="40"/>
+      <c r="D150" s="42"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
     </row>
@@ -4872,34 +4875,34 @@
       <c r="B151" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C151" s="34" t="s">
+      <c r="C151" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D151" s="35"/>
+      <c r="D151" s="37"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
-      <c r="C152" s="36"/>
-      <c r="D152" s="37"/>
+      <c r="C152" s="38"/>
+      <c r="D152" s="39"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
-      <c r="C153" s="36"/>
-      <c r="D153" s="37"/>
+      <c r="C153" s="38"/>
+      <c r="D153" s="39"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
-      <c r="C154" s="36"/>
-      <c r="D154" s="37"/>
+      <c r="C154" s="38"/>
+      <c r="D154" s="39"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
     </row>
@@ -5134,13 +5137,19 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="I52:I55"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="H48:H51"/>
-    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="C151:D151"/>
     <mergeCell ref="C152:D152"/>
     <mergeCell ref="C153:D153"/>
@@ -5150,28 +5159,22 @@
     <mergeCell ref="C148:D148"/>
     <mergeCell ref="C149:D149"/>
     <mergeCell ref="C150:D150"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="I52:I55"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="I48:I51"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="D134:D135"/>
     <mergeCell ref="D136:D137"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="D85:D86"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A115:F115"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="A107:F107"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B44:B45"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
